--- a/docs/export-templates/AI问书_全域模型用量数据导出.xlsx
+++ b/docs/export-templates/AI问书_全域模型用量数据导出.xlsx
@@ -64,7 +64,7 @@
     <t>平台全域模型用量 · 区间指标（近 7 天）</t>
   </si>
   <si>
-    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-09 ~ 2026-07-15） · 机构范围=全部</t>
+    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-31 ~ 2026-08-06） · 机构范围=全部</t>
   </si>
   <si>
     <t>较上一周期</t>
@@ -112,7 +112,7 @@
     <t>模型用量趋势 · 近 7 天</t>
   </si>
   <si>
-    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-09 ~ 2026-07-15）</t>
+    <t>导出时间：2026-07-14 10:00:00 · 统计区间：近 7 天（2026-07-31 ~ 2026-08-06）</t>
   </si>
   <si>
     <t>时间</t>
